--- a/data/dividends_info_20260317.xlsx
+++ b/data/dividends_info_20260317.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>50.84999847412109</v>
+        <v>51.75</v>
       </c>
       <c r="I2" t="n">
-        <v>1.376597878083022</v>
+        <v>1.352657004830918</v>
       </c>
       <c r="J2" t="n">
         <v>342</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>17.89999961853027</v>
+        <v>18.5</v>
       </c>
       <c r="I4" t="n">
-        <v>2.100558703983215</v>
+        <v>2.032432432432433</v>
       </c>
       <c r="J4" t="n">
         <v>125</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>24.55999946594238</v>
+        <v>24.79999923706055</v>
       </c>
       <c r="I5" t="n">
-        <v>3.868078260007193</v>
+        <v>3.830645279135097</v>
       </c>
       <c r="J5" t="n">
         <v>97</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>21.39999961853027</v>
+        <v>21.10000038146973</v>
       </c>
       <c r="I6" t="n">
-        <v>0.911214969514062</v>
+        <v>0.92417059940554</v>
       </c>
       <c r="J6" t="n">
         <v>97</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>63.79999923706055</v>
+        <v>63.31999969482422</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9874608268553735</v>
+        <v>0.9949463092803777</v>
       </c>
       <c r="J7" t="n">
         <v>97</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>21.45000076293945</v>
+        <v>21.70000076293945</v>
       </c>
       <c r="I8" t="n">
-        <v>3.962703821757432</v>
+        <v>3.917050553526617</v>
       </c>
       <c r="J8" t="n">
         <v>97</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6.51200008392334</v>
+        <v>6.579999923706055</v>
       </c>
       <c r="I9" t="n">
-        <v>2.784090873210963</v>
+        <v>2.755319180883613</v>
       </c>
       <c r="J9" t="n">
         <v>97</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.8299999833106995</v>
+        <v>0.859000027179718</v>
       </c>
       <c r="I10" t="n">
-        <v>3.614457904003342</v>
+        <v>3.492432951195177</v>
       </c>
       <c r="J10" t="n">
         <v>76</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>12.36999988555908</v>
+        <v>12.10000038146973</v>
       </c>
       <c r="I11" t="n">
-        <v>2.02101861206849</v>
+        <v>2.066115637342102</v>
       </c>
       <c r="J11" t="n">
         <v>69</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>3.519999980926514</v>
+        <v>3.579999923706055</v>
       </c>
       <c r="I12" t="n">
-        <v>4.261363659454279</v>
+        <v>4.189944223370775</v>
       </c>
       <c r="J12" t="n">
         <v>69</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>9.017999649047852</v>
+        <v>8.060000419616699</v>
       </c>
       <c r="I13" t="n">
-        <v>3.215790766088786</v>
+        <v>3.598014701018975</v>
       </c>
       <c r="J13" t="n">
         <v>62</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>34.56999969482422</v>
+        <v>34.61999893188477</v>
       </c>
       <c r="I14" t="n">
-        <v>4.743997727733676</v>
+        <v>4.737146304443042</v>
       </c>
       <c r="J14" t="n">
         <v>62</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>32.2599983215332</v>
+        <v>33.06999969482422</v>
       </c>
       <c r="I15" t="n">
-        <v>6.199628344881288</v>
+        <v>6.047777497600097</v>
       </c>
       <c r="J15" t="n">
         <v>62</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>3.726000070571899</v>
+        <v>3.710000038146973</v>
       </c>
       <c r="I16" t="n">
-        <v>2.683843212720367</v>
+        <v>2.695417762042581</v>
       </c>
       <c r="J16" t="n">
         <v>62</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>37.95000076293945</v>
+        <v>36.95000076293945</v>
       </c>
       <c r="I17" t="n">
-        <v>0.391198938116967</v>
+        <v>0.4017861892682399</v>
       </c>
       <c r="J17" t="n">
         <v>62</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>22.1200008392334</v>
+        <v>22.34000015258789</v>
       </c>
       <c r="I18" t="n">
-        <v>4.159131849435698</v>
+        <v>4.118173651370483</v>
       </c>
       <c r="J18" t="n">
         <v>62</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>72.04000091552734</v>
+        <v>72.83999633789062</v>
       </c>
       <c r="I19" t="n">
-        <v>1.443642402530621</v>
+        <v>1.427787002041628</v>
       </c>
       <c r="J19" t="n">
         <v>62</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>50.84999847412109</v>
+        <v>51.75</v>
       </c>
       <c r="I20" t="n">
-        <v>4.326450473975212</v>
+        <v>4.251207729468599</v>
       </c>
       <c r="J20" t="n">
         <v>62</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>7.072000026702881</v>
+        <v>7.217999935150146</v>
       </c>
       <c r="I21" t="n">
-        <v>12.16063343824605</v>
+        <v>11.91465790699139</v>
       </c>
       <c r="J21" t="n">
         <v>62</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>10.95499992370605</v>
+        <v>11.02499961853027</v>
       </c>
       <c r="I22" t="n">
-        <v>5.111821121862255</v>
+        <v>5.079365255113295</v>
       </c>
       <c r="J22" t="n">
         <v>62</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1.804999947547913</v>
+        <v>1.809999942779541</v>
       </c>
       <c r="I23" t="n">
-        <v>2.216066546391865</v>
+        <v>2.209944821245335</v>
       </c>
       <c r="J23" t="n">
         <v>62</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>62.5</v>
+        <v>63.40000152587891</v>
       </c>
       <c r="I25" t="n">
-        <v>3.296</v>
+        <v>3.249211278266515</v>
       </c>
       <c r="J25" t="n">
         <v>62</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>14.4399995803833</v>
+        <v>14.53999996185303</v>
       </c>
       <c r="I26" t="n">
-        <v>5.193905968105934</v>
+        <v>5.158184332652622</v>
       </c>
       <c r="J26" t="n">
         <v>62</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>14.84000015258789</v>
+        <v>14.72000026702881</v>
       </c>
       <c r="I27" t="n">
-        <v>2.021563321531935</v>
+        <v>2.038043441289652</v>
       </c>
       <c r="J27" t="n">
         <v>62</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>41.59999847412109</v>
+        <v>40.59999847412109</v>
       </c>
       <c r="I28" t="n">
-        <v>2.043269305715902</v>
+        <v>2.093596137797394</v>
       </c>
       <c r="J28" t="n">
         <v>62</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>32.31999969482422</v>
+        <v>31.6200008392334</v>
       </c>
       <c r="I29" t="n">
-        <v>2.629950519882339</v>
+        <v>2.688171971663387</v>
       </c>
       <c r="J29" t="n">
         <v>62</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>21.52000045776367</v>
+        <v>21.63999938964844</v>
       </c>
       <c r="I31" t="n">
-        <v>4.646840049853412</v>
+        <v>4.621072219060935</v>
       </c>
       <c r="J31" t="n">
         <v>62</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>18.7549991607666</v>
+        <v>18.8700008392334</v>
       </c>
       <c r="I33" t="n">
-        <v>4.212210265797256</v>
+        <v>4.186539294462978</v>
       </c>
       <c r="J33" t="n">
         <v>62</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>4.820000171661377</v>
+        <v>4.429999828338623</v>
       </c>
       <c r="I34" t="n">
-        <v>1.929460512196297</v>
+        <v>2.099322880445295</v>
       </c>
       <c r="J34" t="n">
         <v>62</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1.960000038146973</v>
+        <v>1.904999971389771</v>
       </c>
       <c r="I35" t="n">
-        <v>3.061224430216099</v>
+        <v>3.14960634651494</v>
       </c>
       <c r="J35" t="n">
         <v>62</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>5.114999771118164</v>
+        <v>5.171000003814697</v>
       </c>
       <c r="I36" t="n">
-        <v>3.714565171103909</v>
+        <v>3.674337649581032</v>
       </c>
       <c r="J36" t="n">
         <v>62</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>10.3100004196167</v>
+        <v>10.4399995803833</v>
       </c>
       <c r="I37" t="n">
-        <v>4.190106521994309</v>
+        <v>4.137931200799332</v>
       </c>
       <c r="J37" t="n">
         <v>62</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>24.89999961853027</v>
+        <v>25.29999923706055</v>
       </c>
       <c r="I38" t="n">
-        <v>1.767068300163978</v>
+        <v>1.739130487227323</v>
       </c>
       <c r="J38" t="n">
         <v>62</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>6.579999923706055</v>
+        <v>6.800000190734863</v>
       </c>
       <c r="I39" t="n">
-        <v>7.142857225677318</v>
+        <v>6.911764512012579</v>
       </c>
       <c r="J39" t="n">
         <v>62</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>52.81999969482422</v>
+        <v>52.63999938964844</v>
       </c>
       <c r="I40" t="n">
-        <v>2.6505111853251</v>
+        <v>2.659574498922406</v>
       </c>
       <c r="J40" t="n">
         <v>62</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>2.78600001335144</v>
+        <v>2.828999996185303</v>
       </c>
       <c r="I41" t="n">
-        <v>10.76812629441134</v>
+        <v>10.60445388492498</v>
       </c>
       <c r="J41" t="n">
         <v>62</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>85.05000305175781</v>
+        <v>82.5</v>
       </c>
       <c r="I42" t="n">
-        <v>1.587301530346151</v>
+        <v>1.636363636363636</v>
       </c>
       <c r="J42" t="n">
         <v>62</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>3.381999969482422</v>
+        <v>3.358000040054321</v>
       </c>
       <c r="I43" t="n">
-        <v>5.026611517859258</v>
+        <v>5.062537164152326</v>
       </c>
       <c r="J43" t="n">
         <v>62</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>4.690000057220459</v>
+        <v>4.659999847412109</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8528784544131991</v>
+        <v>0.8583691268190417</v>
       </c>
       <c r="J44" t="n">
         <v>62</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>29.14999961853027</v>
+        <v>28.85000038146973</v>
       </c>
       <c r="I45" t="n">
-        <v>3.602058366177572</v>
+        <v>3.639514683245592</v>
       </c>
       <c r="J45" t="n">
         <v>62</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>23.27000045776367</v>
+        <v>24.11000061035156</v>
       </c>
       <c r="I46" t="n">
-        <v>2.578427108710345</v>
+        <v>2.488593881421934</v>
       </c>
       <c r="J46" t="n">
         <v>62</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>31</v>
+        <v>31.39999961853027</v>
       </c>
       <c r="I47" t="n">
-        <v>1.129032258064516</v>
+        <v>1.114649695070226</v>
       </c>
       <c r="J47" t="n">
         <v>62</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>2.426000118255615</v>
+        <v>2.400000095367432</v>
       </c>
       <c r="I48" t="n">
-        <v>10.71722948583159</v>
+        <v>10.83333290285536</v>
       </c>
       <c r="J48" t="n">
         <v>62</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>14.96000003814697</v>
+        <v>14.46000003814697</v>
       </c>
       <c r="I49" t="n">
-        <v>3.342245980782315</v>
+        <v>3.457814652012091</v>
       </c>
       <c r="J49" t="n">
         <v>55</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>6.639999866485596</v>
+        <v>6.519999980926514</v>
       </c>
       <c r="I50" t="n">
-        <v>3.31325307866973</v>
+        <v>3.374233138705275</v>
       </c>
       <c r="J50" t="n">
         <v>55</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>3.549999952316284</v>
+        <v>3.569999933242798</v>
       </c>
       <c r="I51" t="n">
-        <v>4.507042314059866</v>
+        <v>4.481792800894103</v>
       </c>
       <c r="J51" t="n">
         <v>48</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>18.45999908447266</v>
+        <v>18.86000061035156</v>
       </c>
       <c r="I52" t="n">
-        <v>3.304442200720866</v>
+        <v>3.234358325869795</v>
       </c>
       <c r="J52" t="n">
         <v>48</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>8.539999961853027</v>
+        <v>8.609999656677246</v>
       </c>
       <c r="I53" t="n">
-        <v>5.977751783142052</v>
+        <v>5.929152385088609</v>
       </c>
       <c r="J53" t="n">
         <v>48</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>7.46999979019165</v>
+        <v>7.420000076293945</v>
       </c>
       <c r="I54" t="n">
-        <v>3.614457932843836</v>
+        <v>3.638813978757483</v>
       </c>
       <c r="J54" t="n">
         <v>48</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>4.644999980926514</v>
+        <v>4.619999885559082</v>
       </c>
       <c r="I55" t="n">
-        <v>7.534983884546483</v>
+        <v>7.575757763414864</v>
       </c>
       <c r="J55" t="n">
         <v>48</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>18.5</v>
+        <v>18.79999923706055</v>
       </c>
       <c r="I56" t="n">
-        <v>4.054054054054054</v>
+        <v>3.989361864023487</v>
       </c>
       <c r="J56" t="n">
         <v>48</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>10.10000038146973</v>
+        <v>10.14999961853027</v>
       </c>
       <c r="I57" t="n">
-        <v>4.257425581774359</v>
+        <v>4.23645336119002</v>
       </c>
       <c r="J57" t="n">
         <v>48</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>4.034999847412109</v>
+        <v>4.110000133514404</v>
       </c>
       <c r="I58" t="n">
-        <v>3.717472259539343</v>
+        <v>3.649634917937024</v>
       </c>
       <c r="J58" t="n">
         <v>48</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>11.53999996185303</v>
+        <v>11.52000045776367</v>
       </c>
       <c r="I59" t="n">
-        <v>1.708570196289149</v>
+        <v>1.711536390322988</v>
       </c>
       <c r="J59" t="n">
         <v>48</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>25</v>
+        <v>25.20000076293945</v>
       </c>
       <c r="I60" t="n">
-        <v>4.4</v>
+        <v>4.365079232924955</v>
       </c>
       <c r="J60" t="n">
         <v>48</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>36.65000152587891</v>
+        <v>36.79999923706055</v>
       </c>
       <c r="I61" t="n">
-        <v>1.282401038013951</v>
+        <v>1.277173939521913</v>
       </c>
       <c r="J61" t="n">
         <v>48</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>10.39999961853027</v>
+        <v>10.30000019073486</v>
       </c>
       <c r="I62" t="n">
-        <v>3.653846287868437</v>
+        <v>3.689320320030873</v>
       </c>
       <c r="J62" t="n">
         <v>48</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>27.89999961853027</v>
+        <v>27.54999923706055</v>
       </c>
       <c r="I63" t="n">
-        <v>1.075268831906183</v>
+        <v>1.088929249756337</v>
       </c>
       <c r="J63" t="n">
         <v>48</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>5.840000152587891</v>
+        <v>6.010000228881836</v>
       </c>
       <c r="I64" t="n">
-        <v>2.739725955813527</v>
+        <v>2.662229515917474</v>
       </c>
       <c r="J64" t="n">
         <v>41</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>2.224999904632568</v>
+        <v>2.220000028610229</v>
       </c>
       <c r="I65" t="n">
-        <v>2.921348439820898</v>
+        <v>2.927927890194284</v>
       </c>
       <c r="J65" t="n">
         <v>41</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>7.150000095367432</v>
+        <v>7.210000038146973</v>
       </c>
       <c r="I66" t="n">
-        <v>3.496503449866776</v>
+        <v>3.467406361682239</v>
       </c>
       <c r="J66" t="n">
         <v>41</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>6.579999923706055</v>
+        <v>6.710000038146973</v>
       </c>
       <c r="I67" t="n">
-        <v>7.598784282635446</v>
+        <v>7.451564786251172</v>
       </c>
       <c r="J67" t="n">
         <v>34</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>16.70999908447266</v>
+        <v>17.01000022888184</v>
       </c>
       <c r="I68" t="n">
-        <v>3.889886508755084</v>
+        <v>3.821281547641274</v>
       </c>
       <c r="J68" t="n">
         <v>34</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>11.48499965667725</v>
+        <v>11.65499973297119</v>
       </c>
       <c r="I69" t="n">
-        <v>4.70178507742532</v>
+        <v>4.633204739356426</v>
       </c>
       <c r="J69" t="n">
         <v>34</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>6.046000003814697</v>
+        <v>6.105999946594238</v>
       </c>
       <c r="I70" t="n">
-        <v>1.65398610547313</v>
+        <v>1.63773339133056</v>
       </c>
       <c r="J70" t="n">
         <v>34</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>8.960000038146973</v>
+        <v>8.340000152587891</v>
       </c>
       <c r="I71" t="n">
-        <v>1.785714278111652</v>
+        <v>1.918465192717679</v>
       </c>
       <c r="J71" t="n">
         <v>34</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>288.6000061035156</v>
+        <v>292.7000122070312</v>
       </c>
       <c r="I72" t="n">
-        <v>1.252598726107915</v>
+        <v>1.23505290373649</v>
       </c>
       <c r="J72" t="n">
         <v>34</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>12.88000011444092</v>
+        <v>12.63000011444092</v>
       </c>
       <c r="I74" t="n">
-        <v>4.541925425482755</v>
+        <v>4.631828936653147</v>
       </c>
       <c r="J74" t="n">
         <v>34</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>15.64000034332275</v>
+        <v>15.98499965667725</v>
       </c>
       <c r="I75" t="n">
-        <v>4.028132903903473</v>
+        <v>3.941194954839031</v>
       </c>
       <c r="J75" t="n">
         <v>34</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>98.01999664306641</v>
+        <v>98.08000183105469</v>
       </c>
       <c r="I76" t="n">
-        <v>0.9181799947181114</v>
+        <v>0.91761825366834</v>
       </c>
       <c r="J76" t="n">
         <v>34</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>63.84000015258789</v>
+        <v>64.13999938964844</v>
       </c>
       <c r="I77" t="n">
-        <v>2.695488715361859</v>
+        <v>2.682881222910832</v>
       </c>
       <c r="J77" t="n">
         <v>34</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>23.5</v>
+        <v>22.60000038146973</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5957446808510638</v>
+        <v>0.6194690160925365</v>
       </c>
       <c r="J78" t="n">
         <v>27</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>1.914999961853027</v>
+        <v>1.960000038146973</v>
       </c>
       <c r="I80" t="n">
-        <v>1.775456954427315</v>
+        <v>1.734693843789123</v>
       </c>
       <c r="J80" t="n">
         <v>13</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>22.53499984741211</v>
+        <v>23.34499931335449</v>
       </c>
       <c r="I81" t="n">
-        <v>1.153760824319944</v>
+        <v>1.113728882618845</v>
       </c>
       <c r="J81" t="n">
         <v>6</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>29.3799991607666</v>
+        <v>29.23999977111816</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3063308460545635</v>
+        <v>0.3077975400290446</v>
       </c>
       <c r="J82" t="n">
         <v>6</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>50.84999847412109</v>
+        <v>51.75</v>
       </c>
       <c r="I83" t="n">
-        <v>1.278269458219949</v>
+        <v>1.256038647342995</v>
       </c>
       <c r="J83" t="n">
         <v>-22</v>
@@ -4353,7 +4353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C300"/>
+  <dimension ref="A1:C330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4903,7 +4903,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5056,7 +5056,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5073,7 +5073,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>gAIn360 S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5090,7 +5090,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>gAIn360 S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5107,7 +5107,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Telesia S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5117,14 +5117,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NEXT RE SIIQ S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5134,14 +5134,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>NEXT RE SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5158,7 +5158,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5175,7 +5175,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5192,7 +5192,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5243,7 +5243,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5260,7 +5260,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5277,7 +5277,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5294,7 +5294,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5321,14 +5321,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5345,7 +5345,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5362,7 +5362,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5379,7 +5379,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5396,7 +5396,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5413,7 +5413,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5423,14 +5423,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5447,7 +5447,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5464,7 +5464,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5481,7 +5481,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -5508,14 +5508,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Antares Vision S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5525,14 +5525,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Antares Vision S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5549,7 +5549,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5566,7 +5566,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5576,14 +5576,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5600,7 +5600,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5617,7 +5617,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5634,7 +5634,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5651,7 +5651,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5668,7 +5668,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5685,7 +5685,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5695,14 +5695,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5712,14 +5712,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5746,14 +5746,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5763,14 +5763,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5787,7 +5787,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5804,7 +5804,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5814,14 +5814,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5838,7 +5838,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5848,14 +5848,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5865,14 +5865,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5882,14 +5882,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5899,14 +5899,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5923,7 +5923,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5940,7 +5940,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Braga Moro Sistemi di Energia S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5957,7 +5957,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>Braga Moro Sistemi di Energia S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5974,7 +5974,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6025,7 +6025,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6035,14 +6035,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6059,7 +6059,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6076,7 +6076,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6086,14 +6086,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6110,7 +6110,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6120,14 +6120,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6137,14 +6137,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6161,7 +6161,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6178,7 +6178,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6195,7 +6195,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -6212,7 +6212,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -6229,7 +6229,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -6246,7 +6246,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -6263,7 +6263,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -6273,14 +6273,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -6290,14 +6290,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -6307,14 +6307,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -6331,7 +6331,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -6341,14 +6341,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -6365,7 +6365,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -6375,14 +6375,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -6399,7 +6399,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -6416,7 +6416,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -6433,7 +6433,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -6450,7 +6450,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -6467,7 +6467,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -6477,14 +6477,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -6511,14 +6511,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -6528,14 +6528,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -6562,14 +6562,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6586,7 +6586,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6603,7 +6603,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6620,7 +6620,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6637,7 +6637,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6654,7 +6654,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6671,7 +6671,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6688,7 +6688,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6698,14 +6698,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6722,7 +6722,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6739,7 +6739,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6756,12 +6756,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -6773,29 +6773,29 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -6807,24 +6807,24 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6841,7 +6841,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6858,7 +6858,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6875,7 +6875,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6892,7 +6892,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6909,7 +6909,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6919,14 +6919,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6943,7 +6943,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -6960,7 +6960,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>ELES S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -6977,7 +6977,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -6994,7 +6994,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7011,7 +7011,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7028,7 +7028,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7038,14 +7038,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7062,7 +7062,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7079,7 +7079,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7096,7 +7096,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7113,7 +7113,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7130,7 +7130,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7147,7 +7147,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7164,7 +7164,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7198,7 +7198,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ELES S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7215,7 +7215,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7232,7 +7232,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7249,12 +7249,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -7266,12 +7266,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -7283,12 +7283,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -7300,12 +7300,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -7317,12 +7317,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -7334,12 +7334,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -7351,12 +7351,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -7368,12 +7368,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -7385,12 +7385,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -7402,12 +7402,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -7419,7 +7419,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -7436,7 +7436,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -7446,14 +7446,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -7470,7 +7470,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -7480,14 +7480,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -7504,7 +7504,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -7521,7 +7521,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -7538,7 +7538,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -7555,7 +7555,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -7572,7 +7572,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -7589,7 +7589,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -7606,7 +7606,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -7623,7 +7623,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -7640,7 +7640,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -7657,7 +7657,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -7674,7 +7674,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -7691,7 +7691,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -7708,7 +7708,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -7718,14 +7718,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>HEALTH ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -7742,7 +7742,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -7759,7 +7759,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -7769,14 +7769,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -7786,14 +7786,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -7810,7 +7810,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -7827,7 +7827,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -7844,7 +7844,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -7861,7 +7861,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -7878,7 +7878,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -7895,7 +7895,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>HEALTH ITALIA S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -7912,7 +7912,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -7929,7 +7929,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -7946,12 +7946,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7963,12 +7963,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7980,12 +7980,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7997,12 +7997,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -8014,29 +8014,29 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -8048,12 +8048,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -8065,12 +8065,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -8082,12 +8082,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -8099,12 +8099,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -8116,29 +8116,29 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>NEUROSOFT</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -8150,12 +8150,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -8167,12 +8167,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -8184,12 +8184,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -8201,12 +8201,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -8218,29 +8218,29 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -8252,12 +8252,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -8269,12 +8269,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -8286,7 +8286,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -8303,7 +8303,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -8320,7 +8320,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -8337,7 +8337,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -8354,7 +8354,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -8371,7 +8371,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -8388,7 +8388,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -8405,7 +8405,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -8422,7 +8422,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -8439,7 +8439,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -8456,7 +8456,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -8473,7 +8473,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -8483,14 +8483,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -8500,14 +8500,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -8524,7 +8524,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -8541,7 +8541,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -8558,29 +8558,29 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -8592,12 +8592,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -8609,12 +8609,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -8626,63 +8626,63 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>I.CO.P. S.p.A. Società Benefit</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -8694,63 +8694,63 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -8762,29 +8762,29 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -8796,46 +8796,46 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>RT&amp;L S.P.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>NEUROSOFT</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -8847,148 +8847,148 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>I.CO.P. S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -9000,12 +9000,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -9017,29 +9017,29 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -9051,165 +9051,165 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Autostrade Meridionali S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>TESSELLIS S.p.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>RT&amp;L S.P.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -9221,46 +9221,46 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -9272,12 +9272,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -9289,12 +9289,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -9306,46 +9306,46 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -9357,12 +9357,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -9374,12 +9374,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -9391,29 +9391,29 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -9425,12 +9425,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -9442,15 +9442,525 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
+          <t>TELECOM ITALIA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
           <t>MAIRE S.p.A.</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr">
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Svas Biosana S.p.A.</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>SIT S.p.A.</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>SIT S.p.A.</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Anima Holding S.p.A.</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Autostrade Meridionali S.p.A.</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
         <is>
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="C300" t="inlineStr">
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Banca Generali S.p.A.</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Banco BPM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Basic Net S.p.A.</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>INTERCOS S.p.A.</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>IGD SIIQ S.p.A.</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>FIDIA S.p.A</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Prysmian S.p.A.</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>TESSELLIS S.p.A.</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Seri Industrial S.p.A.</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>BANCA IFIS S.p.A.</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Pirelli &amp; C. S.p.A.</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>OVS S.p.A.</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>MAIRE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>DOTSTAY S.p.A.</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Vimi Fasteners S.p.A.</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Davide Campari-Milano N.V.</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
         <is>
           <t>Annual General Meeting</t>
         </is>
@@ -9467,272 +9977,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Comer Industries S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0005246191</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>41.59999847412109</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>2.043269305715902</v>
-      </c>
-      <c r="I2" t="n">
-        <v>62</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>EL.EN. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>IT0005453250</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-05-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>12.36999988555908</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>2.02101861206849</v>
-      </c>
-      <c r="I3" t="n">
-        <v>69</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>IT0005345233</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>4.820000171661377</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.093</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1.929460512196297</v>
-      </c>
-      <c r="I4" t="n">
-        <v>62</v>
-      </c>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>IRCE s.p.a</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>IT0001077780</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>1.960000038146973</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>3.061224430216099</v>
-      </c>
-      <c r="I5" t="n">
-        <v>62</v>
-      </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Neodecortech S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>IT0005275778</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-05-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>3.519999980926514</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>4.261363659454279</v>
-      </c>
-      <c r="I6" t="n">
-        <v>69</v>
-      </c>
-      <c r="J6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9743,7 +9990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9766,7 +10013,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -9777,329 +10024,6 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Banca Generali S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Banco BPM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Basic Net S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>DOTSTAY S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Davide Campari-Milano N.V.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>FIDIA S.p.A</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>IGD SIIQ S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>INTERCOS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>MAIRE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>OVS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Prysmian S.p.A.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Seri Industrial S.p.A.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>TESMEC S.p.A.</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>TESSELLIS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Vimi Fasteners S.p.A.</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
